--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="468">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -94,9 +94,6 @@
     <t>main.js · VIEW_HINTS</t>
   </si>
   <si>
-    <t>No dedicated story.</t>
-  </si>
-  <si>
     <t>Module tab bar</t>
   </si>
   <si>
@@ -430,9 +427,6 @@
     <t>addModal.js · confirmAddTab()</t>
   </si>
   <si>
-    <t>No matching DevOps story — consider adding to the board.</t>
-  </si>
-  <si>
     <t>Scope &amp; Coverage Tagging</t>
   </si>
   <si>
@@ -604,9 +598,6 @@
     <t>main.js · saveChangesToVersion()</t>
   </si>
   <si>
-    <t>In-place overwrite (distinct from Save As 3250) — no dedicated story.</t>
-  </si>
-  <si>
     <t>localStorage persistence</t>
   </si>
   <si>
@@ -886,7 +877,7 @@
     <t>New Requirement</t>
   </si>
   <si>
-    <t>New requirement — needs a DevOps story.</t>
+    <t>Story 3270 under Feature 3197 (CRE Powered Value Streams Taxonomy). Added to DevOps.</t>
   </si>
   <si>
     <t>Cross-market value-stream validation (US / UK)</t>
@@ -895,12 +886,18 @@
     <t>Confirm that value-stream names and structures are meaningful for both US and UK markets — e.g. "Recoveries" (UK) vs "Service Charges" (US) — and reconcile terminology where they diverge.</t>
   </si>
   <si>
+    <t>Story 3271 under Feature 3197 (CRE Powered Value Streams Taxonomy). Added to DevOps.</t>
+  </si>
+  <si>
     <t>Tagging methodology review and taxonomy alignment</t>
   </si>
   <si>
     <t>Review current scope and coverage tagging to confirm the most appropriate approach, including whether tags should align with the existing taxonomy structure or follow a separate scheme.</t>
   </si>
   <si>
+    <t>Story 3272 under Feature 3205 (Item-Level System Coverage Tag). Added to DevOps.</t>
+  </si>
+  <si>
     <t>Security &amp; Access Control</t>
   </si>
   <si>
@@ -910,7 +907,7 @@
     <t>Define who can change or edit the master copy, whether access should grant editing rights, and the responsibility boundaries between roles (e.g. consultant vs client vs admin).</t>
   </si>
   <si>
-    <t>New requirement — needs a DevOps story. Currently no auth layer exists.</t>
+    <t>Story 3273 under Feature 3269 (Security &amp; Access Control). Added to DevOps.</t>
   </si>
   <si>
     <t>Database persistence (replace localStorage)</t>
@@ -919,13 +916,70 @@
     <t>Move version and taxonomy data from browser localStorage to a database backend so that data persists across browsers, machines, and users.</t>
   </si>
   <si>
-    <t>New requirement — needs a DevOps story. Currently localStorage only.</t>
+    <t>Story 3274 under Feature 3211 (Client Versions). Added to DevOps.</t>
+  </si>
+  <si>
+    <t>Version comparison (side-by-side diff)</t>
+  </si>
+  <si>
+    <t>Side-by-side diff between two saved versions to see what changed from the baseline when tailoring for a client.</t>
+  </si>
+  <si>
+    <t>Nice to Have</t>
+  </si>
+  <si>
+    <t>Future enhancement. Story 3281 under Feature 3211 (Client Versions).</t>
+  </si>
+  <si>
+    <t>Guided discovery workflow</t>
+  </si>
+  <si>
+    <t>Checklist or wizard walking a consultant through module selection, scope tagging, coverage mapping, and export.</t>
+  </si>
+  <si>
+    <t>Future enhancement. Story 3282 under Feature 3195 (View Switcher &amp; Shared Shell).</t>
+  </si>
+  <si>
+    <t>Duplicate a version</t>
+  </si>
+  <si>
+    <t>Clone an existing client version as a starting point for a similar client.</t>
+  </si>
+  <si>
+    <t>Future enhancement. Story 3283 under Feature 3211 (Client Versions).</t>
+  </si>
+  <si>
+    <t>Richer export templates</t>
+  </si>
+  <si>
+    <t>Branded documents with cover page, table of contents, and executive summary.</t>
+  </si>
+  <si>
+    <t>Future enhancement. Story 3284 under Feature 3213 (Word &amp; PDF Export).</t>
+  </si>
+  <si>
+    <t>Progress dashboard</t>
+  </si>
+  <si>
+    <t>In-app view showing discovery completion (% scoped, % mapped, % enriched) per module.</t>
+  </si>
+  <si>
+    <t>Future enhancement. Story 3285 under Feature 3204 (Coverage Mapping Matrix).</t>
+  </si>
+  <si>
+    <t>Attach evidence to processes</t>
+  </si>
+  <si>
+    <t>Link screenshots, documents, or meeting notes to individual processes as supporting artefacts.</t>
+  </si>
+  <si>
+    <t>Future enhancement. Story 3286 under Feature 3210 (Edit Mode Content Authoring).</t>
   </si>
   <si>
     <t>DevOps Backlog ⇄ App Feature Comparison</t>
   </si>
   <si>
-    <t>43 board stories · 39 matched to existing features · 4 on board only · 5 in app only · 5 new requirements. Note: most stories show "New" on the board yet are already implemented in code.</t>
+    <t>54 board stories · 50 matched to existing features · 4 on board only · 0 in app only · 0 new requirements pending. All new requirements and app-only features now have DevOps stories.</t>
   </si>
   <si>
     <t>A · Matched — board story ↔ existing feature</t>
@@ -1207,28 +1261,28 @@
     <t>Future export/import. Confirmed absent (CLAUDE.md). Added to Feature List as Not Started.</t>
   </si>
   <si>
-    <t>C · In app only — built, but no board story</t>
+    <t>C · Previously app-only — now have DevOps stories</t>
   </si>
   <si>
     <t>Note</t>
   </si>
   <si>
-    <t>Minor UX — no story.</t>
-  </si>
-  <si>
-    <t>Esc / Enter / Ctrl+Enter — no story.</t>
-  </si>
-  <si>
-    <t>Notable capability with no story — consider adding to the board.</t>
-  </si>
-  <si>
-    <t>In-place overwrite, distinct from Save As (3250) — no story.</t>
-  </si>
-  <si>
-    <t>Minor UI — no story.</t>
-  </si>
-  <si>
-    <t>D · New requirements — not yet built, not yet on the board</t>
+    <t>Story 3278 created.</t>
+  </si>
+  <si>
+    <t>Story 3279 created.</t>
+  </si>
+  <si>
+    <t>Story 3276 created.</t>
+  </si>
+  <si>
+    <t>Story 3277 created.</t>
+  </si>
+  <si>
+    <t>Story 3280 created.</t>
+  </si>
+  <si>
+    <t>D · New requirements — added to DevOps board</t>
   </si>
   <si>
     <t>Suggested story title</t>
@@ -1243,7 +1297,7 @@
     <t>Standardise value-stream names and descriptions</t>
   </si>
   <si>
-    <t>Add to DevOps board</t>
+    <t>Added: Story 3270</t>
   </si>
   <si>
     <t>Confirm that value-stream names are meaningful for both US and UK markets (e.g. "Recoveries" vs "Service Charges") and reconcile terminology.</t>
@@ -1252,22 +1306,34 @@
     <t>Validate value-stream naming across US/UK markets</t>
   </si>
   <si>
+    <t>Added: Story 3271</t>
+  </si>
+  <si>
     <t>Review scope/coverage tagging approach and confirm whether tags should align with the existing taxonomy structure.</t>
   </si>
   <si>
     <t>Review and align tagging methodology</t>
   </si>
   <si>
+    <t>Added: Story 3272</t>
+  </si>
+  <si>
     <t>Define who can edit the master copy, whether access grants editing rights, and responsibility boundaries between roles.</t>
   </si>
   <si>
     <t>Define security model and access control</t>
   </si>
   <si>
+    <t>Added: Story 3273</t>
+  </si>
+  <si>
     <t>Move data from browser localStorage to a database so it persists across browsers, machines, and users.</t>
   </si>
   <si>
     <t>Add database backend for persistence</t>
+  </si>
+  <si>
+    <t>Added: Story 3274</t>
   </si>
   <si>
     <t>Feature &amp; QA Summary</t>
@@ -1441,45 +1507,45 @@
     <font>
       <b/>
       <color rgb="FF3A5A8A"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="FF2A2A2A"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
       <color rgb="FF888888"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="FF4A7010"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
       <color rgb="FFB8860B"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
       <color rgb="FF4A7010"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
       <color rgb="FFA5342A"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
       <color rgb="FF2A2A2A"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
       <color rgb="FF8B2FC9"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
@@ -2171,7 +2237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2316,11 +2382,11 @@
       <c r="I6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="21" t="s">
-        <v>22</v>
+      <c r="J6" s="21">
+        <v>3278</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2331,13 +2397,13 @@
         <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>17</v>
@@ -2352,7 +2418,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>22</v>
@@ -2366,13 +2432,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>32</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>33</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>17</v>
@@ -2387,7 +2453,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K8" s="22" t="s">
         <v>22</v>
@@ -2401,13 +2467,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>37</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>17</v>
@@ -2422,7 +2488,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>22</v>
@@ -2436,13 +2502,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>41</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>17</v>
@@ -2457,7 +2523,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>22</v>
@@ -2471,13 +2537,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>17</v>
@@ -2491,11 +2557,11 @@
       <c r="I11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="13" t="s">
-        <v>22</v>
+      <c r="J11" s="13">
+        <v>3279</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2503,16 +2569,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>48</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>49</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>17</v>
@@ -2527,7 +2593,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>22</v>
@@ -2538,16 +2604,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>17</v>
@@ -2562,7 +2628,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>22</v>
@@ -2573,16 +2639,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>55</v>
-      </c>
       <c r="E14" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>17</v>
@@ -2597,7 +2663,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>22</v>
@@ -2608,16 +2674,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>17</v>
@@ -2632,7 +2698,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>22</v>
@@ -2643,16 +2709,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>59</v>
-      </c>
       <c r="E16" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>17</v>
@@ -2667,7 +2733,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>22</v>
@@ -2678,16 +2744,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>17</v>
@@ -2702,7 +2768,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>22</v>
@@ -2713,16 +2779,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>67</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>68</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>17</v>
@@ -2737,7 +2803,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>22</v>
@@ -2748,16 +2814,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="E19" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>17</v>
@@ -2772,7 +2838,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K19" s="14" t="s">
         <v>22</v>
@@ -2783,16 +2849,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>74</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>75</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>17</v>
@@ -2807,7 +2873,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>22</v>
@@ -2818,16 +2884,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="E21" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>17</v>
@@ -2842,7 +2908,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K21" s="14" t="s">
         <v>22</v>
@@ -2853,16 +2919,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="19" t="s">
         <v>81</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>82</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>17</v>
@@ -2877,7 +2943,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>22</v>
@@ -2888,16 +2954,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>17</v>
@@ -2912,7 +2978,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K23" s="14" t="s">
         <v>22</v>
@@ -2923,16 +2989,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="E24" s="19" t="s">
         <v>89</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>90</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>17</v>
@@ -2947,7 +3013,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K24" s="22" t="s">
         <v>22</v>
@@ -2958,16 +3024,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>17</v>
@@ -2982,7 +3048,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K25" s="14" t="s">
         <v>22</v>
@@ -2993,16 +3059,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>97</v>
-      </c>
       <c r="E26" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>17</v>
@@ -3017,7 +3083,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K26" s="22" t="s">
         <v>22</v>
@@ -3028,16 +3094,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>17</v>
@@ -3052,7 +3118,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>22</v>
@@ -3063,16 +3129,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="E28" s="19" t="s">
         <v>104</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>105</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>17</v>
@@ -3087,7 +3153,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K28" s="22" t="s">
         <v>22</v>
@@ -3098,16 +3164,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>17</v>
@@ -3122,7 +3188,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K29" s="14" t="s">
         <v>22</v>
@@ -3133,16 +3199,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="E30" s="19" t="s">
         <v>112</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>113</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>17</v>
@@ -3157,7 +3223,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K30" s="22" t="s">
         <v>22</v>
@@ -3168,16 +3234,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>17</v>
@@ -3192,7 +3258,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K31" s="14" t="s">
         <v>22</v>
@@ -3203,16 +3269,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>121</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>122</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>17</v>
@@ -3227,7 +3293,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K32" s="22" t="s">
         <v>22</v>
@@ -3238,16 +3304,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="E33" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>17</v>
@@ -3262,7 +3328,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K33" s="14" t="s">
         <v>22</v>
@@ -3273,16 +3339,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D34" s="18" t="s">
-        <v>128</v>
-      </c>
       <c r="E34" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>17</v>
@@ -3297,7 +3363,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K34" s="22" t="s">
         <v>22</v>
@@ -3308,16 +3374,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="E35" s="9" t="s">
         <v>130</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>131</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>17</v>
@@ -3332,7 +3398,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K35" s="14" t="s">
         <v>22</v>
@@ -3343,16 +3409,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C36" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="E36" s="19" t="s">
         <v>133</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>134</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>17</v>
@@ -3367,7 +3433,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K36" s="22" t="s">
         <v>22</v>
@@ -3378,16 +3444,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="E37" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>17</v>
@@ -3401,11 +3467,11 @@
       <c r="I37" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J37" s="13" t="s">
-        <v>22</v>
+      <c r="J37" s="13">
+        <v>3276</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3413,16 +3479,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="E38" s="19" t="s">
         <v>140</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>142</v>
       </c>
       <c r="F38" s="20" t="s">
         <v>17</v>
@@ -3437,7 +3503,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K38" s="22" t="s">
         <v>22</v>
@@ -3448,16 +3514,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>17</v>
@@ -3472,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K39" s="14" t="s">
         <v>22</v>
@@ -3483,16 +3549,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C40" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>150</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>17</v>
@@ -3507,7 +3573,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K40" s="22" t="s">
         <v>22</v>
@@ -3518,16 +3584,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>17</v>
@@ -3542,7 +3608,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K41" s="14" t="s">
         <v>22</v>
@@ -3553,16 +3619,16 @@
         <v>38</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E42" s="19" t="s">
         <v>156</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>158</v>
       </c>
       <c r="F42" s="20" t="s">
         <v>17</v>
@@ -3577,7 +3643,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K42" s="22" t="s">
         <v>22</v>
@@ -3588,16 +3654,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C43" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>17</v>
@@ -3612,7 +3678,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K43" s="14" t="s">
         <v>22</v>
@@ -3623,16 +3689,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="E44" s="19" t="s">
         <v>165</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>167</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>17</v>
@@ -3647,7 +3713,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K44" s="22" t="s">
         <v>22</v>
@@ -3658,16 +3724,16 @@
         <v>41</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C45" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>17</v>
@@ -3682,7 +3748,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K45" s="14" t="s">
         <v>22</v>
@@ -3693,16 +3759,16 @@
         <v>42</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C46" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" s="19" t="s">
         <v>173</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>175</v>
       </c>
       <c r="F46" s="20" t="s">
         <v>17</v>
@@ -3717,7 +3783,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K46" s="22" t="s">
         <v>22</v>
@@ -3728,16 +3794,16 @@
         <v>43</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C47" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>17</v>
@@ -3752,7 +3818,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K47" s="14" t="s">
         <v>22</v>
@@ -3763,16 +3829,16 @@
         <v>44</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C48" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" s="19" t="s">
         <v>180</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>182</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>17</v>
@@ -3787,7 +3853,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K48" s="22" t="s">
         <v>22</v>
@@ -3798,16 +3864,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="E49" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>17</v>
@@ -3822,7 +3888,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K49" s="14" t="s">
         <v>22</v>
@@ -3833,16 +3899,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C50" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" s="19" t="s">
         <v>189</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>191</v>
       </c>
       <c r="F50" s="20" t="s">
         <v>17</v>
@@ -3857,7 +3923,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K50" s="22" t="s">
         <v>22</v>
@@ -3868,16 +3934,16 @@
         <v>47</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E51" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>17</v>
@@ -3891,11 +3957,11 @@
       <c r="I51" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J51" s="13" t="s">
-        <v>22</v>
+      <c r="J51" s="13">
+        <v>3277</v>
       </c>
       <c r="K51" s="14" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -3903,16 +3969,16 @@
         <v>48</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F52" s="20" t="s">
         <v>17</v>
@@ -3927,7 +3993,7 @@
         <v>20</v>
       </c>
       <c r="J52" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K52" s="22" t="s">
         <v>22</v>
@@ -3938,16 +4004,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>17</v>
@@ -3962,7 +4028,7 @@
         <v>20</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K53" s="14" t="s">
         <v>22</v>
@@ -3973,16 +4039,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F54" s="20" t="s">
         <v>17</v>
@@ -3996,11 +4062,11 @@
       <c r="I54" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J54" s="21" t="s">
-        <v>22</v>
+      <c r="J54" s="21">
+        <v>3280</v>
       </c>
       <c r="K54" s="22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4008,16 +4074,16 @@
         <v>51</v>
       </c>
       <c r="B55" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>17</v>
@@ -4032,7 +4098,7 @@
         <v>20</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K55" s="14" t="s">
         <v>22</v>
@@ -4043,16 +4109,16 @@
         <v>52</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F56" s="20" t="s">
         <v>17</v>
@@ -4067,7 +4133,7 @@
         <v>20</v>
       </c>
       <c r="J56" s="21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K56" s="22" t="s">
         <v>22</v>
@@ -4078,16 +4144,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>17</v>
@@ -4102,7 +4168,7 @@
         <v>20</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K57" s="14" t="s">
         <v>22</v>
@@ -4113,16 +4179,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="E58" s="19" t="s">
         <v>218</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>221</v>
       </c>
       <c r="F58" s="20" t="s">
         <v>17</v>
@@ -4137,10 +4203,10 @@
         <v>20</v>
       </c>
       <c r="J58" s="21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K58" s="22" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4148,16 +4214,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>17</v>
@@ -4172,7 +4238,7 @@
         <v>20</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K59" s="14" t="s">
         <v>22</v>
@@ -4183,16 +4249,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F60" s="20" t="s">
         <v>17</v>
@@ -4207,7 +4273,7 @@
         <v>20</v>
       </c>
       <c r="J60" s="21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K60" s="22" t="s">
         <v>22</v>
@@ -4218,16 +4284,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E61" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>232</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>17</v>
@@ -4242,7 +4308,7 @@
         <v>20</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K61" s="14" t="s">
         <v>22</v>
@@ -4253,16 +4319,16 @@
         <v>58</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F62" s="20" t="s">
         <v>17</v>
@@ -4277,7 +4343,7 @@
         <v>20</v>
       </c>
       <c r="J62" s="21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K62" s="22" t="s">
         <v>22</v>
@@ -4288,16 +4354,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>17</v>
@@ -4312,7 +4378,7 @@
         <v>20</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K63" s="14" t="s">
         <v>22</v>
@@ -4323,16 +4389,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F64" s="20" t="s">
         <v>17</v>
@@ -4347,7 +4413,7 @@
         <v>20</v>
       </c>
       <c r="J64" s="21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K64" s="22" t="s">
         <v>22</v>
@@ -4358,16 +4424,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>17</v>
@@ -4382,7 +4448,7 @@
         <v>20</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K65" s="14" t="s">
         <v>22</v>
@@ -4393,16 +4459,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F66" s="20" t="s">
         <v>17</v>
@@ -4417,7 +4483,7 @@
         <v>20</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K66" s="22" t="s">
         <v>22</v>
@@ -4428,16 +4494,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>17</v>
@@ -4452,7 +4518,7 @@
         <v>20</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K67" s="14" t="s">
         <v>22</v>
@@ -4463,16 +4529,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F68" s="20" t="s">
         <v>17</v>
@@ -4487,7 +4553,7 @@
         <v>20</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K68" s="22" t="s">
         <v>22</v>
@@ -4498,16 +4564,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>260</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>17</v>
@@ -4522,7 +4588,7 @@
         <v>20</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K69" s="14" t="s">
         <v>22</v>
@@ -4533,16 +4599,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F70" s="20" t="s">
         <v>17</v>
@@ -4557,7 +4623,7 @@
         <v>20</v>
       </c>
       <c r="J70" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K70" s="22" t="s">
         <v>22</v>
@@ -4571,16 +4637,16 @@
         <v>13</v>
       </c>
       <c r="C71" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F71" s="25" t="s">
         <v>264</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="F71" s="25" t="s">
-        <v>267</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>18</v>
@@ -4592,10 +4658,10 @@
         <v>20</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K71" s="14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4603,22 +4669,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C72" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="F72" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="G72" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="F72" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="G72" s="12" t="s">
-        <v>273</v>
       </c>
       <c r="H72" s="20" t="s">
         <v>19</v>
@@ -4627,10 +4693,10 @@
         <v>20</v>
       </c>
       <c r="J72" s="21" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K72" s="22" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4638,34 +4704,34 @@
         <v>69</v>
       </c>
       <c r="B73" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="F73" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="I73" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="K73" s="14" t="s">
         <v>279</v>
-      </c>
-      <c r="F73" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="K73" s="14" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4673,34 +4739,34 @@
         <v>70</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C74" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="F74" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="K74" s="22" t="s">
         <v>283</v>
-      </c>
-      <c r="D74" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="F74" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H74" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="K74" s="22" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4708,34 +4774,34 @@
         <v>71</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C75" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="13">
+        <v>3270</v>
+      </c>
+      <c r="K75" s="14" t="s">
         <v>287</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J75" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K75" s="14" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4743,31 +4809,31 @@
         <v>72</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I76" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J76" s="21" t="s">
-        <v>22</v>
+      <c r="J76" s="21">
+        <v>3271</v>
       </c>
       <c r="K76" s="22" t="s">
         <v>290</v>
@@ -4778,34 +4844,34 @@
         <v>73</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C77" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="13">
+        <v>3272</v>
+      </c>
+      <c r="K77" s="14" t="s">
         <v>293</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="F77" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="G77" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="I77" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J77" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K77" s="14" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4813,34 +4879,34 @@
         <v>74</v>
       </c>
       <c r="B78" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="C78" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="D78" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="D78" s="18" t="s">
+      <c r="E78" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="F78" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="H78" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="21">
+        <v>3273</v>
+      </c>
+      <c r="K78" s="22" t="s">
         <v>297</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="F78" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H78" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J78" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="K78" s="22" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -4848,34 +4914,244 @@
         <v>75</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C79" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D79" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="E79" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" s="13">
+        <v>3274</v>
+      </c>
+      <c r="K79" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="F79" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J79" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K79" s="14" t="s">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>76</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>301</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="13">
+        <v>3281</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>77</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="13">
+        <v>3282</v>
+      </c>
+      <c r="K81" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>78</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="13">
+        <v>3283</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>79</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="13">
+        <v>3284</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>80</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="13">
+        <v>3285</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>81</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" s="13">
+        <v>3286</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -4911,7 +5187,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4932,7 +5208,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -4945,7 +5221,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -4958,7 +5234,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -4971,28 +5247,28 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>22</v>
@@ -5003,13 +5279,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E5" s="33">
         <v>3</v>
@@ -5018,7 +5294,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H5" s="32" t="s">
         <v>22</v>
@@ -5026,25 +5302,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E6" s="38">
         <v>2</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H6" s="37" t="s">
         <v>22</v>
@@ -5052,25 +5328,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E7" s="33">
         <v>2</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H7" s="32" t="s">
         <v>22</v>
@@ -5078,25 +5354,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E8" s="38">
         <v>3</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H8" s="37" t="s">
         <v>22</v>
@@ -5104,25 +5380,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E9" s="33">
         <v>3</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H9" s="32" t="s">
         <v>22</v>
@@ -5130,25 +5406,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E10" s="38">
         <v>2</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>22</v>
@@ -5156,25 +5432,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E11" s="33">
         <v>3</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H11" s="32" t="s">
         <v>22</v>
@@ -5182,25 +5458,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E12" s="38">
         <v>3</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>22</v>
@@ -5208,25 +5484,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E13" s="33">
         <v>2</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H13" s="32" t="s">
         <v>22</v>
@@ -5234,25 +5510,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E14" s="38">
         <v>2</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H14" s="37" t="s">
         <v>22</v>
@@ -5260,25 +5536,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E15" s="33">
         <v>2</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>22</v>
@@ -5286,25 +5562,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="37" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>333</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>315</v>
       </c>
       <c r="E16" s="38">
         <v>3</v>
       </c>
       <c r="F16" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="G16" s="35" t="s">
         <v>334</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>316</v>
       </c>
       <c r="H16" s="37" t="s">
         <v>22</v>
@@ -5312,25 +5588,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E17" s="33">
         <v>3</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H17" s="32" t="s">
         <v>22</v>
@@ -5338,129 +5614,129 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="E18" s="38">
         <v>3</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="E19" s="33">
         <v>3</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="E20" s="38">
         <v>5</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="E21" s="33">
         <v>3</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E22" s="38">
         <v>5</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H22" s="37" t="s">
         <v>22</v>
@@ -5468,25 +5744,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E23" s="33">
         <v>3</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H23" s="32" t="s">
         <v>22</v>
@@ -5494,25 +5770,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E24" s="38">
         <v>3</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G24" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H24" s="37" t="s">
         <v>22</v>
@@ -5520,25 +5796,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E25" s="33">
         <v>3</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G25" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H25" s="32" t="s">
         <v>22</v>
@@ -5546,51 +5822,51 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E26" s="38">
         <v>2</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="G26" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E27" s="33">
         <v>3</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>22</v>
@@ -5598,25 +5874,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E28" s="38">
         <v>3</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>22</v>
@@ -5624,25 +5900,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E29" s="33">
         <v>3</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="G29" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H29" s="32" t="s">
         <v>22</v>
@@ -5650,25 +5926,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E30" s="38">
         <v>3</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H30" s="37" t="s">
         <v>22</v>
@@ -5676,25 +5952,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E31" s="33">
         <v>5</v>
       </c>
       <c r="F31" s="32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G31" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H31" s="32" t="s">
         <v>22</v>
@@ -5702,25 +5978,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="36" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E32" s="38">
         <v>3</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G32" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H32" s="37" t="s">
         <v>22</v>
@@ -5728,25 +6004,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E33" s="33">
         <v>3</v>
       </c>
       <c r="F33" s="32" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H33" s="32" t="s">
         <v>22</v>
@@ -5754,25 +6030,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E34" s="38">
         <v>5</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="G34" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H34" s="37" t="s">
         <v>22</v>
@@ -5780,25 +6056,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E35" s="33">
         <v>5</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="G35" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H35" s="32" t="s">
         <v>22</v>
@@ -5806,25 +6082,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E36" s="38">
         <v>3</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G36" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H36" s="37" t="s">
         <v>22</v>
@@ -5832,25 +6108,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E37" s="33">
         <v>5</v>
       </c>
       <c r="F37" s="32" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="G37" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H37" s="32" t="s">
         <v>22</v>
@@ -5858,25 +6134,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E38" s="38">
         <v>3</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G38" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H38" s="37" t="s">
         <v>22</v>
@@ -5884,25 +6160,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E39" s="33">
         <v>3</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G39" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H39" s="32" t="s">
         <v>22</v>
@@ -5910,25 +6186,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E40" s="38">
         <v>2</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="G40" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H40" s="37" t="s">
         <v>22</v>
@@ -5936,51 +6212,51 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E41" s="33">
         <v>3</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="G41" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E42" s="38">
         <v>5</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="G42" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H42" s="37" t="s">
         <v>22</v>
@@ -5988,25 +6264,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="31" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E43" s="33">
         <v>3</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H43" s="32" t="s">
         <v>22</v>
@@ -6014,7 +6290,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="B45" s="44"/>
       <c r="C45" s="44"/>
@@ -6027,25 +6303,25 @@
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="30" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="G46" s="30" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="H46" s="30" t="s">
         <v>22</v>
@@ -6056,107 +6332,107 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="31" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E47" s="33">
         <v>2</v>
       </c>
       <c r="F47" s="45" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="G47" s="32" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="H47" s="32"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="31" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E48" s="33">
         <v>2</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="G48" s="32" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="H48" s="32"/>
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E49" s="33">
         <v>8</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="G49" s="32" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="H49" s="32"/>
       <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="31" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E50" s="33">
         <v>5</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="G50" s="32" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="H50" s="32"/>
       <c r="I50" s="32"/>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
@@ -6178,7 +6454,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E53" s="30" t="s">
         <v>22</v>
@@ -6207,7 +6483,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E54" s="32"/>
       <c r="F54" s="32"/>
@@ -6217,16 +6493,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B55" s="32" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
@@ -6236,16 +6512,16 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="32"/>
@@ -6255,16 +6531,16 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="B57" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="C57" s="49" t="s">
-        <v>195</v>
-      </c>
       <c r="D57" s="32" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="E57" s="32"/>
       <c r="F57" s="32"/>
@@ -6274,16 +6550,16 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="48" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E58" s="32"/>
       <c r="F58" s="32"/>
@@ -6293,7 +6569,7 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="50" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="B60" s="50"/>
       <c r="C60" s="50"/>
@@ -6315,13 +6591,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="E61" s="30" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="G61" s="30" t="s">
         <v>22</v>
@@ -6335,22 +6611,22 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="48" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="E62" s="51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F62" s="52" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="G62" s="52"/>
       <c r="H62" s="52"/>
@@ -6358,22 +6634,22 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="48" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B63" s="32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="E63" s="51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F63" s="52" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="G63" s="52"/>
       <c r="H63" s="52"/>
@@ -6381,22 +6657,22 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="48" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="E64" s="51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F64" s="52" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="G64" s="52"/>
       <c r="H64" s="52"/>
@@ -6404,22 +6680,22 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="48" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B65" s="32" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F65" s="52" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="G65" s="52"/>
       <c r="H65" s="52"/>
@@ -6427,22 +6703,22 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="48" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B66" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C66" s="32" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F66" s="52" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="G66" s="52"/>
       <c r="H66" s="52"/>
@@ -6472,7 +6748,7 @@
     <mergeCell ref="F66:I66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6488,14 +6764,14 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="B3" s="54"/>
       <c r="C3" s="54"/>
@@ -6505,10 +6781,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -6524,7 +6800,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="B6" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"In Progress")</f>
@@ -6535,7 +6811,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B7" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"Not Started")</f>
@@ -6546,7 +6822,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="B8" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"Backlog")</f>
@@ -6557,7 +6833,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="B9" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"Blocked")</f>
@@ -6568,7 +6844,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="B10" s="60">
         <f>COUNTA('Feature List'!$G$5:$G$79)</f>
@@ -6589,10 +6865,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -6608,7 +6884,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="B15" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$79,"In Progress")</f>
@@ -6619,7 +6895,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="56" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="B16" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$79,"Passed")</f>
@@ -6630,7 +6906,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="B17" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$79,"Failed")</f>
@@ -6641,7 +6917,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="B18" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$79,"Blocked")</f>
@@ -6652,7 +6928,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="B19" s="60">
         <f>COUNTA('Feature List'!$I$5:$I$79)</f>
@@ -6673,10 +6949,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -6692,7 +6968,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B24" s="57">
         <f>COUNTIF('Feature List'!$F$5:$F$79,"DevOps Backlog")</f>
@@ -6703,7 +6979,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="56" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B25" s="57">
         <f>COUNTIF('Feature List'!$F$5:$F$79,"New Requirement")</f>
@@ -6714,7 +6990,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="B26" s="60">
         <f>COUNTA('Feature List'!$F$5:$F$79)</f>
@@ -6725,30 +7001,30 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="62" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="B28" s="62"/>
       <c r="C28" s="62"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="56" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="B29" s="57">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="56" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="B30" s="57">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="56" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="B31" s="57">
         <v>4</v>
@@ -6756,23 +7032,23 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="56" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B32" s="57">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="56" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="B33" s="57">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="56" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="B34" s="57">
         <v>35</v>
@@ -6787,7 +7063,7 @@
     <mergeCell ref="A28:C28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6802,16 +7078,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="B1" s="53"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6819,7 +7095,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6827,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6835,7 +7111,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6843,7 +7119,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6851,7 +7127,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6859,15 +7135,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -6875,6 +7151,6 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="475">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -343,9 +343,18 @@
     <t>mappingView.js · showCell()</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
     <t>3236</t>
   </si>
   <si>
+    <t>Tested 2026-08-18</t>
+  </si>
+  <si>
     <t>Coverage colour coding</t>
   </si>
   <si>
@@ -814,7 +823,7 @@
     <t>3220</t>
   </si>
   <si>
-    <t>Implemented in CSS; was absent from the original feature list.</t>
+    <t>Implemented in CSS; was absent from the original feature list. | Tested 2026-08-18</t>
   </si>
   <si>
     <t>Placeholder modules flagged (awaiting SME review)</t>
@@ -877,7 +886,7 @@
     <t>New Requirement</t>
   </si>
   <si>
-    <t>Story 3270 under Feature 3197 (CRE Powered Value Streams Taxonomy). Added to DevOps.</t>
+    <t>Story 3270 under Feature 3197 (CRE Powered Value Streams Taxonomy). Added to DevOps. | Tested 2026-08-18</t>
   </si>
   <si>
     <t>Cross-market value-stream validation (US / UK)</t>
@@ -946,7 +955,7 @@
     <t>Clone an existing client version as a starting point for a similar client.</t>
   </si>
   <si>
-    <t>Future enhancement. Story 3283 under Feature 3211 (Client Versions).</t>
+    <t>Future enhancement. Story 3283 under Feature 3211 (Client Versions). | Tested 2026-08-18</t>
   </si>
   <si>
     <t>Richer export templates</t>
@@ -974,6 +983,18 @@
   </si>
   <si>
     <t>Future enhancement. Story 3286 under Feature 3210 (Edit Mode Content Authoring).</t>
+  </si>
+  <si>
+    <t>Search / filter versions</t>
+  </si>
+  <si>
+    <t>Allow users to search or filter the versions list by name so they can quickly locate a saved client version when the list is long.</t>
+  </si>
+  <si>
+    <t>3287</t>
+  </si>
+  <si>
+    <t>Added 2026-08-18. Future enhancement — search/filter versions panel when version count grows.</t>
   </si>
   <si>
     <t>DevOps Backlog ⇄ App Feature Comparison</t>
@@ -1424,7 +1445,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1483,6 +1504,10 @@
       <b/>
       <color rgb="FF1A5FA8"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -1565,7 +1590,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1589,17 +1614,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3F0D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
+        <fgColor rgb="FFF7F7F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1620,6 +1650,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8B2FC9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1698,7 +1733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1727,9 +1762,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1757,9 +1789,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1778,23 +1807,20 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
@@ -1802,13 +1828,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1817,10 +1843,10 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1829,67 +1855,73 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="26" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="27" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2237,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2344,48 +2376,48 @@
       <c r="H5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="13" t="s">
+      <c r="I5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="21">
+      <c r="I6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="19">
         <v>3278</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2393,7 +2425,7 @@
       <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -2414,48 +2446,48 @@
       <c r="H7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="13" t="s">
+      <c r="I7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="21" t="s">
+      <c r="I8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2463,7 +2495,7 @@
       <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -2484,48 +2516,48 @@
       <c r="H9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="13" t="s">
+      <c r="I9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="21" t="s">
+      <c r="I10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2533,7 +2565,7 @@
       <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -2554,48 +2586,48 @@
       <c r="H11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="13">
+      <c r="I11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="12">
         <v>3279</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>8</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="21" t="s">
+      <c r="I12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2603,7 +2635,7 @@
       <c r="A13" s="5">
         <v>9</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="21" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -2624,48 +2656,48 @@
       <c r="H13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="13" t="s">
+      <c r="I13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="21" t="s">
+      <c r="I14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2673,7 +2705,7 @@
       <c r="A15" s="5">
         <v>11</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="21" t="s">
         <v>45</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -2694,48 +2726,48 @@
       <c r="H15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="13" t="s">
+      <c r="I15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="21" t="s">
+      <c r="I16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2743,7 +2775,7 @@
       <c r="A17" s="5">
         <v>13</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="21" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -2764,48 +2796,48 @@
       <c r="H17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="13" t="s">
+      <c r="I17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>14</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="21" t="s">
+      <c r="I18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="K18" s="22" t="s">
+      <c r="K18" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2813,7 +2845,7 @@
       <c r="A19" s="5">
         <v>15</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="21" t="s">
         <v>64</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -2834,48 +2866,48 @@
       <c r="H19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="13" t="s">
+      <c r="I19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="21" t="s">
+      <c r="I20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="22" t="s">
+      <c r="K20" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2883,7 +2915,7 @@
       <c r="A21" s="5">
         <v>17</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="21" t="s">
         <v>64</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -2904,48 +2936,48 @@
       <c r="H21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="13" t="s">
+      <c r="I21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="H22" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="21" t="s">
+      <c r="I22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="K22" s="22" t="s">
+      <c r="K22" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2953,7 +2985,7 @@
       <c r="A23" s="5">
         <v>19</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="21" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -2974,48 +3006,48 @@
       <c r="H23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="I23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="K23" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
-        <v>20</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="A24" s="14">
+        <v>20</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="21" t="s">
+      <c r="I24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="K24" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3023,7 +3055,7 @@
       <c r="A25" s="5">
         <v>21</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="21" t="s">
         <v>64</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -3044,48 +3076,48 @@
       <c r="H25" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="13" t="s">
+      <c r="I25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="K25" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
-        <v>22</v>
-      </c>
-      <c r="B26" s="16" t="s">
+      <c r="A26" s="14">
+        <v>22</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="H26" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="21" t="s">
+      <c r="I26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="22" t="s">
+      <c r="K26" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3114,48 +3146,48 @@
       <c r="H27" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I27" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="13" t="s">
+      <c r="I27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="K27" s="14" t="s">
+      <c r="K27" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="21" t="s">
+      <c r="I28" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="K28" s="22" t="s">
+      <c r="K28" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3163,7 +3195,7 @@
       <c r="A29" s="5">
         <v>25</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="21" t="s">
         <v>97</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -3182,50 +3214,50 @@
         <v>18</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="K29" s="14" t="s">
-        <v>22</v>
+      <c r="I29" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="15">
+      <c r="A30" s="14">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" s="20" t="s">
+      <c r="C30" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I30" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="K30" s="22" t="s">
+      <c r="I30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="K30" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3233,17 +3265,17 @@
       <c r="A31" s="5">
         <v>27</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="21" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>17</v>
@@ -3252,50 +3284,50 @@
         <v>18</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>22</v>
+        <v>109</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="15">
+      <c r="A32" s="14">
         <v>28</v>
       </c>
-      <c r="B32" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E32" s="19" t="s">
+      <c r="B32" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="C32" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="K32" s="22" t="s">
+      <c r="I32" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K32" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3303,17 +3335,17 @@
       <c r="A33" s="5">
         <v>29</v>
       </c>
-      <c r="B33" s="23" t="s">
-        <v>118</v>
+      <c r="B33" s="21" t="s">
+        <v>121</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>17</v>
@@ -3324,48 +3356,48 @@
       <c r="H33" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I33" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="K33" s="14" t="s">
+      <c r="I33" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K33" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="15">
+      <c r="A34" s="14">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F34" s="20" t="s">
+      <c r="B34" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="20" t="s">
+      <c r="H34" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I34" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="K34" s="22" t="s">
+      <c r="I34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3373,17 +3405,17 @@
       <c r="A35" s="5">
         <v>31</v>
       </c>
-      <c r="B35" s="23" t="s">
-        <v>118</v>
+      <c r="B35" s="21" t="s">
+        <v>121</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>17</v>
@@ -3394,48 +3426,48 @@
       <c r="H35" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I35" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="K35" s="14" t="s">
+      <c r="I35" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K35" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="15">
+      <c r="A36" s="14">
         <v>32</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="F36" s="20" t="s">
+      <c r="B36" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H36" s="20" t="s">
+      <c r="H36" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I36" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="K36" s="22" t="s">
+      <c r="I36" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K36" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3443,17 +3475,17 @@
       <c r="A37" s="5">
         <v>33</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>118</v>
+      <c r="B37" s="21" t="s">
+        <v>121</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>17</v>
@@ -3464,48 +3496,48 @@
       <c r="H37" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I37" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="13">
+      <c r="I37" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="12">
         <v>3276</v>
       </c>
-      <c r="K37" s="14" t="s">
+      <c r="K37" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="15">
+      <c r="A38" s="14">
         <v>34</v>
       </c>
-      <c r="B38" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E38" s="19" t="s">
+      <c r="B38" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="C38" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="20" t="s">
+      <c r="H38" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="K38" s="22" t="s">
+      <c r="I38" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="K38" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3513,17 +3545,17 @@
       <c r="A39" s="5">
         <v>35</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>137</v>
+      <c r="B39" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>17</v>
@@ -3534,48 +3566,48 @@
       <c r="H39" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="K39" s="14" t="s">
+      <c r="I39" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="15">
+      <c r="A40" s="14">
         <v>36</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C40" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F40" s="20" t="s">
+      <c r="B40" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="20" t="s">
+      <c r="H40" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I40" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="K40" s="22" t="s">
+      <c r="I40" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="K40" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3583,17 +3615,17 @@
       <c r="A41" s="5">
         <v>37</v>
       </c>
-      <c r="B41" s="23" t="s">
-        <v>137</v>
+      <c r="B41" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>17</v>
@@ -3604,48 +3636,48 @@
       <c r="H41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I41" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="K41" s="14" t="s">
+      <c r="I41" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="K41" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
+      <c r="A42" s="14">
         <v>38</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="F42" s="20" t="s">
+      <c r="B42" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H42" s="20" t="s">
+      <c r="H42" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="K42" s="22" t="s">
+      <c r="I42" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="K42" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3653,17 +3685,17 @@
       <c r="A43" s="5">
         <v>39</v>
       </c>
-      <c r="B43" s="23" t="s">
-        <v>137</v>
+      <c r="B43" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>17</v>
@@ -3674,66 +3706,66 @@
       <c r="H43" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I43" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K43" s="14" t="s">
+      <c r="I43" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="K43" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="15">
+      <c r="A44" s="14">
         <v>40</v>
       </c>
-      <c r="B44" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E44" s="19" t="s">
+      <c r="B44" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="C44" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H44" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="K44" s="22" t="s">
-        <v>22</v>
+      <c r="H44" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>41</v>
       </c>
-      <c r="B45" s="23" t="s">
-        <v>162</v>
+      <c r="B45" s="21" t="s">
+        <v>165</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>17</v>
@@ -3742,68 +3774,68 @@
         <v>18</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>22</v>
+        <v>109</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K45" s="13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="15">
+      <c r="A46" s="14">
         <v>42</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="F46" s="20" t="s">
+      <c r="B46" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="K46" s="22" t="s">
-        <v>22</v>
+      <c r="H46" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J46" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>43</v>
       </c>
-      <c r="B47" s="23" t="s">
-        <v>162</v>
+      <c r="B47" s="21" t="s">
+        <v>165</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>17</v>
@@ -3814,48 +3846,48 @@
       <c r="H47" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I47" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="K47" s="14" t="s">
+      <c r="I47" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="K47" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="15">
+      <c r="A48" s="14">
         <v>44</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="F48" s="20" t="s">
+      <c r="B48" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H48" s="20" t="s">
+      <c r="H48" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I48" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J48" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="K48" s="22" t="s">
+      <c r="I48" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="K48" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3864,16 +3896,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>17</v>
@@ -3884,66 +3916,66 @@
       <c r="H49" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I49" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J49" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="K49" s="14" t="s">
+      <c r="I49" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="K49" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
+      <c r="A50" s="14">
         <v>46</v>
       </c>
-      <c r="B50" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="F50" s="20" t="s">
+      <c r="B50" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H50" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="K50" s="22" t="s">
-        <v>22</v>
+      <c r="H50" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>47</v>
       </c>
-      <c r="B51" s="23" t="s">
-        <v>182</v>
+      <c r="B51" s="21" t="s">
+        <v>185</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>17</v>
@@ -3954,48 +3986,48 @@
       <c r="H51" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I51" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" s="13">
+      <c r="I51" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="12">
         <v>3277</v>
       </c>
-      <c r="K51" s="14" t="s">
+      <c r="K51" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="15">
+      <c r="A52" s="14">
         <v>48</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="F52" s="20" t="s">
+      <c r="B52" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H52" s="20" t="s">
+      <c r="H52" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J52" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="K52" s="22" t="s">
+      <c r="I52" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="K52" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4003,17 +4035,17 @@
       <c r="A53" s="5">
         <v>49</v>
       </c>
-      <c r="B53" s="23" t="s">
-        <v>182</v>
+      <c r="B53" s="21" t="s">
+        <v>185</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>17</v>
@@ -4024,48 +4056,48 @@
       <c r="H53" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I53" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="K53" s="14" t="s">
+      <c r="I53" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="K53" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="15">
+      <c r="A54" s="14">
         <v>50</v>
       </c>
-      <c r="B54" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="F54" s="20" t="s">
+      <c r="B54" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H54" s="20" t="s">
+      <c r="H54" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I54" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J54" s="21">
+      <c r="I54" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="19">
         <v>3280</v>
       </c>
-      <c r="K54" s="22" t="s">
+      <c r="K54" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4074,16 +4106,16 @@
         <v>51</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>17</v>
@@ -4094,48 +4126,48 @@
       <c r="H55" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I55" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="K55" s="14" t="s">
+      <c r="I55" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K55" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="15">
+      <c r="A56" s="14">
         <v>52</v>
       </c>
-      <c r="B56" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="F56" s="20" t="s">
+      <c r="B56" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="F56" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H56" s="20" t="s">
+      <c r="H56" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J56" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="K56" s="22" t="s">
+      <c r="I56" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="K56" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4143,17 +4175,17 @@
       <c r="A57" s="5">
         <v>53</v>
       </c>
-      <c r="B57" s="23" t="s">
-        <v>203</v>
+      <c r="B57" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>17</v>
@@ -4164,66 +4196,66 @@
       <c r="H57" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="K57" s="14" t="s">
+      <c r="I57" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="K57" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="15">
+      <c r="A58" s="14">
         <v>54</v>
       </c>
-      <c r="B58" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="E58" s="19" t="s">
+      <c r="B58" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="C58" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F58" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="20" t="s">
+      <c r="H58" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I58" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J58" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="K58" s="22" t="s">
-        <v>220</v>
+      <c r="I58" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="K58" s="20" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>55</v>
       </c>
-      <c r="B59" s="23" t="s">
-        <v>215</v>
+      <c r="B59" s="21" t="s">
+        <v>218</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>17</v>
@@ -4234,48 +4266,48 @@
       <c r="H59" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I59" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="K59" s="14" t="s">
+      <c r="I59" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="K59" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="15">
+      <c r="A60" s="14">
         <v>56</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="F60" s="20" t="s">
+      <c r="B60" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="F60" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="20" t="s">
+      <c r="H60" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I60" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="K60" s="22" t="s">
+      <c r="I60" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="K60" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4284,16 +4316,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>17</v>
@@ -4304,48 +4336,48 @@
       <c r="H61" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I61" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J61" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="K61" s="14" t="s">
+      <c r="I61" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="K61" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="15">
+      <c r="A62" s="14">
         <v>58</v>
       </c>
-      <c r="B62" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F62" s="20" t="s">
+      <c r="B62" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="F62" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H62" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I62" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J62" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="K62" s="22" t="s">
+      <c r="I62" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="K62" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4353,17 +4385,17 @@
       <c r="A63" s="5">
         <v>59</v>
       </c>
-      <c r="B63" s="23" t="s">
-        <v>226</v>
+      <c r="B63" s="21" t="s">
+        <v>229</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>17</v>
@@ -4374,48 +4406,48 @@
       <c r="H63" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I63" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J63" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="K63" s="14" t="s">
+      <c r="I63" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="K63" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="15">
+      <c r="A64" s="14">
         <v>60</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="F64" s="20" t="s">
+      <c r="B64" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H64" s="20" t="s">
+      <c r="H64" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I64" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J64" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="K64" s="22" t="s">
+      <c r="I64" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="K64" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4423,17 +4455,17 @@
       <c r="A65" s="5">
         <v>61</v>
       </c>
-      <c r="B65" s="23" t="s">
-        <v>226</v>
+      <c r="B65" s="21" t="s">
+        <v>229</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>17</v>
@@ -4444,48 +4476,48 @@
       <c r="H65" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I65" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J65" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="K65" s="14" t="s">
+      <c r="I65" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="K65" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="15">
+      <c r="A66" s="14">
         <v>62</v>
       </c>
-      <c r="B66" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="F66" s="20" t="s">
+      <c r="B66" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="F66" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H66" s="20" t="s">
+      <c r="H66" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I66" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J66" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="K66" s="22" t="s">
+      <c r="I66" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="K66" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4493,17 +4525,17 @@
       <c r="A67" s="5">
         <v>63</v>
       </c>
-      <c r="B67" s="23" t="s">
-        <v>226</v>
+      <c r="B67" s="21" t="s">
+        <v>229</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>17</v>
@@ -4514,48 +4546,48 @@
       <c r="H67" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I67" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J67" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="K67" s="14" t="s">
+      <c r="I67" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="K67" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="15">
+      <c r="A68" s="14">
         <v>64</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="F68" s="20" t="s">
+      <c r="B68" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="F68" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H68" s="20" t="s">
+      <c r="H68" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I68" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J68" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="K68" s="22" t="s">
+      <c r="I68" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="K68" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4564,16 +4596,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>17</v>
@@ -4584,48 +4616,48 @@
       <c r="H69" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I69" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J69" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="K69" s="14" t="s">
+      <c r="I69" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="K69" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="15">
+      <c r="A70" s="14">
         <v>66</v>
       </c>
-      <c r="B70" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="E70" s="19" t="s">
+      <c r="B70" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E70" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F70" s="20" t="s">
+      <c r="F70" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H70" s="20" t="s">
+      <c r="H70" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I70" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J70" s="21" t="s">
+      <c r="I70" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="K70" s="22" t="s">
+      <c r="K70" s="20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4637,66 +4669,66 @@
         <v>13</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="F71" s="25" t="s">
-        <v>264</v>
+        <v>266</v>
+      </c>
+      <c r="F71" s="23" t="s">
+        <v>267</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="K71" s="13" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="14">
+        <v>68</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="F72" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H72" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I71" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J71" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="K71" s="14" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="15">
-        <v>68</v>
-      </c>
-      <c r="B72" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C72" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="F72" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="G72" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="H72" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J72" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="K72" s="22" t="s">
-        <v>272</v>
+      <c r="I72" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="K72" s="20" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4704,69 +4736,69 @@
         <v>69</v>
       </c>
       <c r="B73" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C73" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="F73" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>270</v>
-      </c>
       <c r="H73" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="K73" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="14">
+        <v>70</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="E74" s="18" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="15">
-        <v>70</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="C74" s="17" t="s">
+      <c r="F74" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H74" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="D74" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="F74" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="H74" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="K74" s="22" t="s">
-        <v>283</v>
+      <c r="I74" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4777,66 +4809,66 @@
         <v>64</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>270</v>
+        <v>289</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>273</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J75" s="13">
+        <v>109</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J75" s="12">
         <v>3270</v>
       </c>
-      <c r="K75" s="14" t="s">
-        <v>287</v>
+      <c r="K75" s="13" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="15">
+      <c r="A76" s="14">
         <v>72</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C76" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="D76" s="18" t="s">
+      <c r="C76" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="F76" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="E76" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="H76" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J76" s="21">
+      <c r="G76" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="19">
         <v>3271</v>
       </c>
-      <c r="K76" s="22" t="s">
-        <v>290</v>
+      <c r="K76" s="20" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4844,69 +4876,69 @@
         <v>73</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="G77" s="12" t="s">
-        <v>270</v>
+        <v>289</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>273</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="I77" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J77" s="13">
+        <v>280</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="12">
         <v>3272</v>
       </c>
-      <c r="K77" s="14" t="s">
-        <v>293</v>
+      <c r="K77" s="13" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="15">
+      <c r="A78" s="14">
         <v>74</v>
       </c>
-      <c r="B78" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="C78" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="F78" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="H78" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J78" s="21">
+      <c r="B78" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D78" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="19">
         <v>3273</v>
       </c>
-      <c r="K78" s="22" t="s">
-        <v>297</v>
+      <c r="K78" s="20" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -4914,34 +4946,34 @@
         <v>75</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>270</v>
+        <v>289</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>273</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J79" s="13">
+        <v>280</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" s="12">
         <v>3274</v>
       </c>
-      <c r="K79" s="14" t="s">
-        <v>300</v>
+      <c r="K79" s="13" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -4949,34 +4981,34 @@
         <v>76</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I80" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J80" s="13">
+      <c r="J80" s="12">
         <v>3281</v>
       </c>
-      <c r="K80" s="14" t="s">
-        <v>304</v>
+      <c r="K80" s="13" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -4987,31 +5019,31 @@
         <v>13</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D81" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F81" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="E81" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>303</v>
-      </c>
       <c r="G81" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I81" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J81" s="13">
+      <c r="J81" s="12">
         <v>3282</v>
       </c>
-      <c r="K81" s="14" t="s">
-        <v>307</v>
+      <c r="K81" s="13" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5019,34 +5051,34 @@
         <v>78</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J82" s="13">
+        <v>110</v>
+      </c>
+      <c r="J82" s="12">
         <v>3283</v>
       </c>
-      <c r="K82" s="14" t="s">
-        <v>310</v>
+      <c r="K82" s="13" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5054,34 +5086,34 @@
         <v>79</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J83" s="13">
+      <c r="J83" s="12">
         <v>3284</v>
       </c>
-      <c r="K83" s="14" t="s">
-        <v>313</v>
+      <c r="K83" s="13" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5092,31 +5124,31 @@
         <v>97</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J84" s="13">
+      <c r="J84" s="12">
         <v>3285</v>
       </c>
-      <c r="K84" s="14" t="s">
-        <v>316</v>
+      <c r="K84" s="13" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5124,34 +5156,69 @@
         <v>81</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J85" s="13">
+      <c r="J85" s="12">
         <v>3286</v>
       </c>
-      <c r="K85" s="14" t="s">
-        <v>319</v>
+      <c r="K85" s="13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="25">
+        <v>82</v>
+      </c>
+      <c r="B86" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="D86" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="E86" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="G86" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="H86" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="I86" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="K86" s="25" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -5207,1522 +5274,1522 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>320</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
+      <c r="A1" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
+      <c r="A2" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="A3" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>327</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="H4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="B4" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E5" s="32">
+        <v>3</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E6" s="37">
+        <v>2</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E7" s="32">
+        <v>2</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>346</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E8" s="37">
+        <v>3</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E9" s="32">
+        <v>3</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>350</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>351</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E10" s="37">
+        <v>2</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E11" s="32">
+        <v>3</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12" s="37">
+        <v>3</v>
+      </c>
+      <c r="F12" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" s="32">
+        <v>2</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" s="37">
+        <v>2</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>357</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E15" s="32">
+        <v>2</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E16" s="37">
+        <v>3</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E17" s="32">
+        <v>3</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="E18" s="37">
+        <v>3</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>363</v>
+      </c>
+      <c r="E19" s="32">
+        <v>3</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>368</v>
+      </c>
+      <c r="E20" s="37">
+        <v>5</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>369</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="E21" s="32">
+        <v>3</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E22" s="37">
+        <v>5</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E23" s="32">
+        <v>3</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E24" s="37">
+        <v>3</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E25" s="32">
+        <v>3</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H25" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E26" s="37">
+        <v>2</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>382</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H26" s="36" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E27" s="32">
+        <v>3</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E28" s="37">
+        <v>3</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H28" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E29" s="32">
+        <v>3</v>
+      </c>
+      <c r="F29" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E30" s="37">
+        <v>3</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H30" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E31" s="32">
+        <v>5</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H31" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E32" s="37">
+        <v>3</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H32" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E33" s="32">
+        <v>3</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E34" s="37">
+        <v>5</v>
+      </c>
+      <c r="F34" s="36" t="s">
+        <v>395</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H34" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E35" s="32">
+        <v>5</v>
+      </c>
+      <c r="F35" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H35" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>399</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D36" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E36" s="37">
+        <v>3</v>
+      </c>
+      <c r="F36" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H36" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E37" s="32">
+        <v>5</v>
+      </c>
+      <c r="F37" s="31" t="s">
+        <v>401</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H37" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" s="36" t="s">
+        <v>402</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D38" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E38" s="37">
+        <v>3</v>
+      </c>
+      <c r="F38" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="G38" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H38" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E39" s="32">
+        <v>3</v>
+      </c>
+      <c r="F39" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H39" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E40" s="37">
+        <v>2</v>
+      </c>
+      <c r="F40" s="36" t="s">
+        <v>405</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H40" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E41" s="32">
+        <v>3</v>
+      </c>
+      <c r="F41" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="G41" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H41" s="31" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="D42" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="E42" s="37">
+        <v>5</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H42" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E43" s="32">
+        <v>3</v>
+      </c>
+      <c r="F43" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="H43" s="31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="43" t="s">
+        <v>412</v>
+      </c>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B46" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C46" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D46" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E46" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="F46" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="H46" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="D47" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="E47" s="32">
+        <v>2</v>
+      </c>
+      <c r="F47" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>414</v>
+      </c>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>415</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="E48" s="32">
+        <v>2</v>
+      </c>
+      <c r="F48" s="45" t="s">
+        <v>416</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>417</v>
+      </c>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>418</v>
+      </c>
+      <c r="D49" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="E49" s="32">
+        <v>8</v>
+      </c>
+      <c r="F49" s="45" t="s">
+        <v>416</v>
+      </c>
+      <c r="G49" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>418</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="E50" s="32">
+        <v>5</v>
+      </c>
+      <c r="F50" s="45" t="s">
+        <v>416</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+    </row>
+    <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="46" t="s">
+        <v>422</v>
+      </c>
+      <c r="B52" s="46"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E6" s="38">
-        <v>2</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E7" s="33">
-        <v>2</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>339</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>340</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E8" s="38">
+      <c r="C53" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>423</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="E56" s="31"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="D58" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+    </row>
+    <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="49" t="s">
+        <v>429</v>
+      </c>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E9" s="33">
-        <v>3</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E10" s="38">
-        <v>2</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>345</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E11" s="33">
-        <v>3</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>346</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E12" s="38">
-        <v>3</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>347</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E13" s="33">
-        <v>2</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>349</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E14" s="38">
-        <v>2</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>350</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="33">
-        <v>2</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E16" s="38">
-        <v>3</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>353</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E17" s="33">
-        <v>3</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>354</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>356</v>
-      </c>
-      <c r="E18" s="38">
-        <v>3</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>356</v>
-      </c>
-      <c r="E19" s="33">
-        <v>3</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>361</v>
-      </c>
-      <c r="E20" s="38">
+      <c r="C61" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>361</v>
-      </c>
-      <c r="E21" s="33">
-        <v>3</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="37" t="s">
-        <v>367</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E22" s="38">
-        <v>5</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E23" s="33">
-        <v>3</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E24" s="38">
-        <v>3</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="G24" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D25" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E25" s="33">
-        <v>3</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="G25" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
-        <v>373</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>374</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E26" s="38">
-        <v>2</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E27" s="33">
-        <v>3</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="B28" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E28" s="38">
-        <v>3</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
-        <v>379</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E29" s="33">
-        <v>3</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="G29" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="B30" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E30" s="38">
-        <v>3</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G30" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>383</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D31" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E31" s="33">
-        <v>5</v>
-      </c>
-      <c r="F31" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="G31" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="B32" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>348</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E32" s="38">
-        <v>3</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="G32" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E33" s="33">
-        <v>3</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="G33" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H33" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
-        <v>386</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>387</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E34" s="38">
-        <v>5</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>388</v>
-      </c>
-      <c r="G34" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
-        <v>389</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>390</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E35" s="33">
-        <v>5</v>
-      </c>
-      <c r="F35" s="32" t="s">
-        <v>391</v>
-      </c>
-      <c r="G35" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H35" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="B36" s="37" t="s">
-        <v>392</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D36" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E36" s="38">
-        <v>3</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="G36" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="B37" s="32" t="s">
-        <v>393</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="D37" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E37" s="33">
-        <v>5</v>
-      </c>
-      <c r="F37" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="G37" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H37" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="B38" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D38" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E38" s="38">
-        <v>3</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="G38" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="B39" s="32" t="s">
-        <v>396</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D39" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E39" s="33">
-        <v>3</v>
-      </c>
-      <c r="F39" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="G39" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="B40" s="37" t="s">
-        <v>397</v>
-      </c>
-      <c r="C40" s="38" t="s">
-        <v>348</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E40" s="38">
-        <v>2</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>398</v>
-      </c>
-      <c r="G40" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B41" s="32" t="s">
-        <v>399</v>
-      </c>
-      <c r="C41" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="D41" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E41" s="33">
-        <v>3</v>
-      </c>
-      <c r="F41" s="32" t="s">
-        <v>400</v>
-      </c>
-      <c r="G41" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H41" s="32" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="B42" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="C42" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D42" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E42" s="38">
-        <v>5</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="G42" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="B43" s="32" t="s">
-        <v>404</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D43" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E43" s="33">
-        <v>3</v>
-      </c>
-      <c r="F43" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G43" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="44" t="s">
-        <v>405</v>
-      </c>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
-    </row>
-    <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B46" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>327</v>
-      </c>
-      <c r="F46" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="G46" s="30" t="s">
-        <v>406</v>
-      </c>
-      <c r="H46" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="B47" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>333</v>
-      </c>
-      <c r="E47" s="33">
-        <v>2</v>
-      </c>
-      <c r="F47" s="45" t="s">
-        <v>334</v>
-      </c>
-      <c r="G47" s="32" t="s">
-        <v>407</v>
-      </c>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="B48" s="32" t="s">
-        <v>408</v>
-      </c>
-      <c r="C48" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>333</v>
-      </c>
-      <c r="E48" s="33">
-        <v>2</v>
-      </c>
-      <c r="F48" s="46" t="s">
-        <v>409</v>
-      </c>
-      <c r="G48" s="32" t="s">
-        <v>410</v>
-      </c>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="B49" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>333</v>
-      </c>
-      <c r="E49" s="33">
+      <c r="D61" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="E61" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="46" t="s">
-        <v>409</v>
-      </c>
-      <c r="G49" s="32" t="s">
-        <v>412</v>
-      </c>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="B50" s="32" t="s">
-        <v>413</v>
-      </c>
-      <c r="C50" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>333</v>
-      </c>
-      <c r="E50" s="33">
-        <v>5</v>
-      </c>
-      <c r="F50" s="46" t="s">
-        <v>409</v>
-      </c>
-      <c r="G50" s="32" t="s">
-        <v>414</v>
-      </c>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-    </row>
-    <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="47" t="s">
-        <v>415</v>
-      </c>
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
-      <c r="I52" s="47"/>
-    </row>
-    <row r="53" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="E53" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="F53" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="B54" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>417</v>
-      </c>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="32" t="s">
-        <v>418</v>
-      </c>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="B56" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D56" s="32" t="s">
-        <v>419</v>
-      </c>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="48" t="s">
-        <v>191</v>
-      </c>
-      <c r="B57" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C57" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="D57" s="32" t="s">
-        <v>420</v>
-      </c>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="B58" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C58" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>421</v>
-      </c>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-    </row>
-    <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B60" s="50"/>
-      <c r="C60" s="50"/>
-      <c r="D60" s="50"/>
-      <c r="E60" s="50"/>
-      <c r="F60" s="50"/>
-      <c r="G60" s="50"/>
-      <c r="H60" s="50"/>
-      <c r="I60" s="50"/>
-    </row>
-    <row r="61" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="E61" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="G61" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" s="30" t="s">
+      <c r="F61" s="29" t="s">
+        <v>431</v>
+      </c>
+      <c r="G61" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="48" t="s">
-        <v>284</v>
-      </c>
-      <c r="B62" s="32" t="s">
+      <c r="A62" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="B62" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C62" s="32" t="s">
-        <v>425</v>
-      </c>
-      <c r="D62" s="32" t="s">
-        <v>426</v>
-      </c>
-      <c r="E62" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="F62" s="52" t="s">
-        <v>427</v>
-      </c>
-      <c r="G62" s="52"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="52"/>
+      <c r="C62" s="31" t="s">
+        <v>432</v>
+      </c>
+      <c r="D62" s="31" t="s">
+        <v>433</v>
+      </c>
+      <c r="E62" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F62" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="G62" s="51"/>
+      <c r="H62" s="51"/>
+      <c r="I62" s="51"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="48" t="s">
-        <v>288</v>
-      </c>
-      <c r="B63" s="32" t="s">
+      <c r="A63" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="B63" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="32" t="s">
-        <v>428</v>
-      </c>
-      <c r="D63" s="32" t="s">
-        <v>429</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="F63" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="G63" s="52"/>
-      <c r="H63" s="52"/>
-      <c r="I63" s="52"/>
+      <c r="C63" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="D63" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F63" s="51" t="s">
+        <v>437</v>
+      </c>
+      <c r="G63" s="51"/>
+      <c r="H63" s="51"/>
+      <c r="I63" s="51"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="48" t="s">
-        <v>291</v>
-      </c>
-      <c r="B64" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C64" s="32" t="s">
-        <v>431</v>
-      </c>
-      <c r="D64" s="32" t="s">
-        <v>432</v>
-      </c>
-      <c r="E64" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="F64" s="52" t="s">
-        <v>433</v>
-      </c>
-      <c r="G64" s="52"/>
-      <c r="H64" s="52"/>
-      <c r="I64" s="52"/>
+      <c r="A64" s="47" t="s">
+        <v>294</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="31" t="s">
+        <v>438</v>
+      </c>
+      <c r="D64" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="E64" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F64" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="G64" s="51"/>
+      <c r="H64" s="51"/>
+      <c r="I64" s="51"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="48" t="s">
-        <v>295</v>
-      </c>
-      <c r="B65" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="C65" s="32" t="s">
-        <v>434</v>
-      </c>
-      <c r="D65" s="32" t="s">
-        <v>435</v>
-      </c>
-      <c r="E65" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="F65" s="52" t="s">
-        <v>436</v>
-      </c>
-      <c r="G65" s="52"/>
-      <c r="H65" s="52"/>
-      <c r="I65" s="52"/>
+      <c r="A65" s="47" t="s">
+        <v>298</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="C65" s="31" t="s">
+        <v>441</v>
+      </c>
+      <c r="D65" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="E65" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F65" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="G65" s="51"/>
+      <c r="H65" s="51"/>
+      <c r="I65" s="51"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="48" t="s">
-        <v>298</v>
-      </c>
-      <c r="B66" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C66" s="32" t="s">
-        <v>437</v>
-      </c>
-      <c r="D66" s="32" t="s">
-        <v>438</v>
-      </c>
-      <c r="E66" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="F66" s="52" t="s">
-        <v>439</v>
-      </c>
-      <c r="G66" s="52"/>
-      <c r="H66" s="52"/>
-      <c r="I66" s="52"/>
+      <c r="A66" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="C66" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="D66" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="E66" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F66" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="G66" s="51"/>
+      <c r="H66" s="51"/>
+      <c r="I66" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -6763,294 +6830,294 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>440</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
+      <c r="A1" s="52" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
-        <v>441</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
+      <c r="A3" s="53" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="55" t="s">
-        <v>442</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>443</v>
+      <c r="B4" s="54" t="s">
+        <v>449</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="57">
+      <c r="B5" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"Done")</f>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="57">
         <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Done")/COUNTA('Feature List'!$G$5:$G$79))</f>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
-        <v>444</v>
-      </c>
-      <c r="B6" s="57">
+      <c r="A6" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"In Progress")</f>
       </c>
-      <c r="C6" s="58">
+      <c r="C6" s="57">
         <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"In Progress")/COUNTA('Feature List'!$G$5:$G$79))</f>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="57">
+      <c r="A7" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"Not Started")</f>
       </c>
-      <c r="C7" s="58">
+      <c r="C7" s="57">
         <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Not Started")/COUNTA('Feature List'!$G$5:$G$79))</f>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
-        <v>445</v>
-      </c>
-      <c r="B8" s="57">
+      <c r="A8" s="55" t="s">
+        <v>452</v>
+      </c>
+      <c r="B8" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"Backlog")</f>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="57">
         <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Backlog")/COUNTA('Feature List'!$G$5:$G$79))</f>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="B9" s="57">
+      <c r="A9" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="B9" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$79,"Blocked")</f>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="57">
         <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Blocked")/COUNTA('Feature List'!$G$5:$G$79))</f>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="59" t="s">
-        <v>447</v>
-      </c>
-      <c r="B10" s="60">
+      <c r="A10" s="58" t="s">
+        <v>454</v>
+      </c>
+      <c r="B10" s="59">
         <f>COUNTA('Feature List'!$G$5:$G$79)</f>
       </c>
-      <c r="C10" s="61">
+      <c r="C10" s="60">
         <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,1)</f>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="55" t="s">
-        <v>442</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>443</v>
+      <c r="B13" s="54" t="s">
+        <v>449</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="57">
+      <c r="A14" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$79,"Not Tested")</f>
       </c>
-      <c r="C14" s="58">
+      <c r="C14" s="57">
         <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Not Tested")/COUNTA('Feature List'!$I$5:$I$79))</f>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
-        <v>444</v>
-      </c>
-      <c r="B15" s="57">
+      <c r="A15" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="B15" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$79,"In Progress")</f>
       </c>
-      <c r="C15" s="58">
+      <c r="C15" s="57">
         <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"In Progress")/COUNTA('Feature List'!$I$5:$I$79))</f>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
-        <v>448</v>
-      </c>
-      <c r="B16" s="57">
+      <c r="A16" s="55" t="s">
+        <v>455</v>
+      </c>
+      <c r="B16" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$79,"Passed")</f>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="57">
         <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Passed")/COUNTA('Feature List'!$I$5:$I$79))</f>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="55" t="s">
+        <v>456</v>
+      </c>
+      <c r="B17" s="56">
+        <f>COUNTIF('Feature List'!$I$5:$I$79,"Failed")</f>
+      </c>
+      <c r="C17" s="57">
+        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Failed")/COUNTA('Feature List'!$I$5:$I$79))</f>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="B18" s="56">
+        <f>COUNTIF('Feature List'!$I$5:$I$79,"Blocked")</f>
+      </c>
+      <c r="C18" s="57">
+        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Blocked")/COUNTA('Feature List'!$I$5:$I$79))</f>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="58" t="s">
+        <v>454</v>
+      </c>
+      <c r="B19" s="59">
+        <f>COUNTA('Feature List'!$I$5:$I$79)</f>
+      </c>
+      <c r="C19" s="60">
+        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,1)</f>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="54" t="s">
         <v>449</v>
       </c>
-      <c r="B17" s="57">
-        <f>COUNTIF('Feature List'!$I$5:$I$79,"Failed")</f>
-      </c>
-      <c r="C17" s="58">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Failed")/COUNTA('Feature List'!$I$5:$I$79))</f>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="B18" s="57">
-        <f>COUNTIF('Feature List'!$I$5:$I$79,"Blocked")</f>
-      </c>
-      <c r="C18" s="58">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Blocked")/COUNTA('Feature List'!$I$5:$I$79))</f>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="59" t="s">
-        <v>447</v>
-      </c>
-      <c r="B19" s="60">
-        <f>COUNTA('Feature List'!$I$5:$I$79)</f>
-      </c>
-      <c r="C19" s="61">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,1)</f>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="55" t="s">
-        <v>442</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>443</v>
+      <c r="C22" s="54" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="57">
+      <c r="B23" s="56">
         <f>COUNTIF('Feature List'!$F$5:$F$79,"Existing")</f>
       </c>
-      <c r="C23" s="58">
+      <c r="C23" s="57">
         <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,COUNTIF('Feature List'!$F$5:$F$79,"Existing")/COUNTA('Feature List'!$F$5:$F$79))</f>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="56" t="s">
-        <v>264</v>
-      </c>
-      <c r="B24" s="57">
+      <c r="A24" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="56">
         <f>COUNTIF('Feature List'!$F$5:$F$79,"DevOps Backlog")</f>
       </c>
-      <c r="C24" s="58">
+      <c r="C24" s="57">
         <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,COUNTIF('Feature List'!$F$5:$F$79,"DevOps Backlog")/COUNTA('Feature List'!$F$5:$F$79))</f>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
-        <v>286</v>
-      </c>
-      <c r="B25" s="57">
+      <c r="A25" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="B25" s="56">
         <f>COUNTIF('Feature List'!$F$5:$F$79,"New Requirement")</f>
       </c>
-      <c r="C25" s="58">
+      <c r="C25" s="57">
         <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,COUNTIF('Feature List'!$F$5:$F$79,"New Requirement")/COUNTA('Feature List'!$F$5:$F$79))</f>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="59" t="s">
-        <v>447</v>
-      </c>
-      <c r="B26" s="60">
+      <c r="A26" s="58" t="s">
+        <v>454</v>
+      </c>
+      <c r="B26" s="59">
         <f>COUNTA('Feature List'!$F$5:$F$79)</f>
       </c>
-      <c r="C26" s="61">
+      <c r="C26" s="60">
         <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,1)</f>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="62" t="s">
-        <v>450</v>
-      </c>
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
+      <c r="A28" s="61" t="s">
+        <v>457</v>
+      </c>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="56" t="s">
-        <v>451</v>
-      </c>
-      <c r="B29" s="57">
+      <c r="A29" s="55" t="s">
+        <v>458</v>
+      </c>
+      <c r="B29" s="56">
         <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="56" t="s">
-        <v>452</v>
-      </c>
-      <c r="B30" s="57">
+      <c r="A30" s="55" t="s">
+        <v>459</v>
+      </c>
+      <c r="B30" s="56">
         <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="56" t="s">
-        <v>453</v>
-      </c>
-      <c r="B31" s="57">
+      <c r="A31" s="55" t="s">
+        <v>460</v>
+      </c>
+      <c r="B31" s="56">
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
-        <v>454</v>
-      </c>
-      <c r="B32" s="57">
+      <c r="A32" s="55" t="s">
+        <v>461</v>
+      </c>
+      <c r="B32" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="56" t="s">
-        <v>455</v>
-      </c>
-      <c r="B33" s="57">
+      <c r="A33" s="55" t="s">
+        <v>462</v>
+      </c>
+      <c r="B33" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="56" t="s">
-        <v>456</v>
-      </c>
-      <c r="B34" s="57">
+      <c r="A34" s="55" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34" s="56">
         <v>35</v>
       </c>
     </row>
@@ -7077,73 +7144,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>457</v>
-      </c>
-      <c r="B1" s="53"/>
+      <c r="A1" s="52" t="s">
+        <v>464</v>
+      </c>
+      <c r="B1" s="52"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
-        <v>458</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>459</v>
+      <c r="A3" s="62" t="s">
+        <v>465</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="66" t="s">
-        <v>460</v>
+      <c r="B4" s="65" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="66" t="s">
-        <v>461</v>
+      <c r="B5" s="65" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="66" t="s">
-        <v>462</v>
+      <c r="B6" s="65" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="66" t="s">
-        <v>463</v>
+      <c r="B7" s="65" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="66" t="s">
-        <v>464</v>
+      <c r="B8" s="65" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="66" t="s">
-        <v>465</v>
+      <c r="B9" s="65" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="65" t="s">
-        <v>466</v>
-      </c>
-      <c r="B10" s="66" t="s">
-        <v>467</v>
+      <c r="A10" s="64" t="s">
+        <v>473</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>
